--- a/experiment/Omni_2CH_bestx4/Test/results-Urban100/Urban100.xlsx
+++ b/experiment/Omni_2CH_bestx4/Test/results-Urban100/Urban100.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27.58</v>
+        <v>27.63</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7662</v>
+        <v>0.7677</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26.75</v>
+        <v>26.8</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8179</v>
+        <v>0.8204</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.96</v>
+        <v>23.98</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6911</v>
+        <v>0.6929</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.11</v>
+        <v>23.23</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8318</v>
+        <v>0.8349</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28.22</v>
+        <v>28.41</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9520999999999999</v>
+        <v>0.9536</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22.56</v>
+        <v>22.58</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6288</v>
+        <v>0.6304</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29.62</v>
+        <v>29.65</v>
       </c>
       <c r="C8" t="n">
-        <v>0.863</v>
+        <v>0.8639</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21.55</v>
+        <v>21.54</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6681</v>
+        <v>0.6713</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>33.91</v>
+        <v>33.95</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9278999999999999</v>
+        <v>0.9288999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27.44</v>
+        <v>27.55</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8911</v>
+        <v>0.8927</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17.82</v>
+        <v>17.96</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7853</v>
+        <v>0.7887</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23.97</v>
+        <v>23.96</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7381</v>
+        <v>0.7399</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29.65</v>
+        <v>29.69</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8401</v>
+        <v>0.8421999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22.43</v>
+        <v>22.45</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6901</v>
+        <v>0.6925</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>26.32</v>
+        <v>26.37</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7387</v>
+        <v>0.7411</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>30.54</v>
+        <v>30.62</v>
       </c>
       <c r="C17" t="n">
-        <v>0.916</v>
+        <v>0.9167999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25.89</v>
+        <v>25.94</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8314</v>
+        <v>0.8333</v>
       </c>
     </row>
     <row r="19">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>22.25</v>
+        <v>22.3</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8181</v>
+        <v>0.8198</v>
       </c>
     </row>
     <row r="21">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22.2</v>
+        <v>22.23</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7223000000000001</v>
+        <v>0.7241</v>
       </c>
     </row>
     <row r="22">
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>29.7</v>
+        <v>29.69</v>
       </c>
       <c r="C22" t="n">
         <v>0.785</v>
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>26.12</v>
+        <v>26.14</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7611</v>
+        <v>0.7625999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>30.52</v>
+        <v>30.58</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9159</v>
+        <v>0.918</v>
       </c>
     </row>
     <row r="25">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>20.54</v>
+        <v>20.59</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6677</v>
+        <v>0.6722</v>
       </c>
     </row>
     <row r="26">
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>31.99</v>
+        <v>32.11</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9</v>
+        <v>0.9013</v>
       </c>
     </row>
     <row r="27">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>27.97</v>
+        <v>28</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7034</v>
+        <v>0.705</v>
       </c>
     </row>
     <row r="28">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28.39</v>
+        <v>28.4</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7981</v>
+        <v>0.7989000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>31.4</v>
+        <v>31.42</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8748</v>
+        <v>0.8752</v>
       </c>
     </row>
     <row r="30">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>27.17</v>
+        <v>27.22</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8682</v>
+        <v>0.8699</v>
       </c>
     </row>
     <row r="31">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>24.74</v>
+        <v>24.81</v>
       </c>
       <c r="C31" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8171</v>
       </c>
     </row>
     <row r="32">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>24.31</v>
+        <v>24.32</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7925</v>
+        <v>0.7942</v>
       </c>
     </row>
     <row r="33">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>29.05</v>
+        <v>29.13</v>
       </c>
       <c r="C33" t="n">
-        <v>0.8534</v>
+        <v>0.8565</v>
       </c>
     </row>
     <row r="34">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>27.24</v>
+        <v>27.33</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8028</v>
+        <v>0.8070000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>23.1</v>
+        <v>23.11</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5878</v>
+        <v>0.589</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>29.3</v>
+        <v>29.41</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8797</v>
+        <v>0.8822</v>
       </c>
     </row>
     <row r="37">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>28.93</v>
+        <v>28.97</v>
       </c>
       <c r="C37" t="n">
-        <v>0.8879</v>
+        <v>0.8888</v>
       </c>
     </row>
     <row r="38">
@@ -923,7 +923,7 @@
         <v>26.6</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8038</v>
+        <v>0.8046</v>
       </c>
     </row>
     <row r="39">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>27.13</v>
+        <v>27.16</v>
       </c>
       <c r="C39" t="n">
-        <v>0.6853</v>
+        <v>0.6894</v>
       </c>
     </row>
     <row r="40">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>23.13</v>
+        <v>23.17</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7499</v>
+        <v>0.7519</v>
       </c>
     </row>
     <row r="41">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>28</v>
+        <v>28.04</v>
       </c>
       <c r="C41" t="n">
-        <v>0.947</v>
+        <v>0.9474</v>
       </c>
     </row>
     <row r="42">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>26.6</v>
+        <v>26.61</v>
       </c>
       <c r="C42" t="n">
-        <v>0.8866000000000001</v>
+        <v>0.8881</v>
       </c>
     </row>
     <row r="43">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>29.05</v>
+        <v>29.03</v>
       </c>
       <c r="C43" t="n">
-        <v>0.8892</v>
+        <v>0.8891</v>
       </c>
     </row>
     <row r="44">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>32.36</v>
+        <v>32.48</v>
       </c>
       <c r="C44" t="n">
-        <v>0.9341</v>
+        <v>0.9351</v>
       </c>
     </row>
     <row r="45">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>31.88</v>
+        <v>32.03</v>
       </c>
       <c r="C45" t="n">
-        <v>0.868</v>
+        <v>0.8702</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>24.11</v>
+        <v>24.21</v>
       </c>
       <c r="C46" t="n">
-        <v>0.7145</v>
+        <v>0.7215</v>
       </c>
     </row>
     <row r="47">
@@ -1040,7 +1040,7 @@
         <v>23.74</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7635999999999999</v>
+        <v>0.7634</v>
       </c>
     </row>
     <row r="48">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>22.11</v>
+        <v>22.16</v>
       </c>
       <c r="C48" t="n">
-        <v>0.7806999999999999</v>
+        <v>0.7834</v>
       </c>
     </row>
     <row r="49">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>20.61</v>
+        <v>20.65</v>
       </c>
       <c r="C49" t="n">
-        <v>0.8243</v>
+        <v>0.825</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>23.64</v>
+        <v>23.68</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7542</v>
+        <v>0.756</v>
       </c>
     </row>
     <row r="51">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>25.35</v>
+        <v>25.4</v>
       </c>
       <c r="C51" t="n">
-        <v>0.7737000000000001</v>
+        <v>0.7768</v>
       </c>
     </row>
     <row r="52">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>27.54</v>
+        <v>27.58</v>
       </c>
       <c r="C52" t="n">
-        <v>0.8512999999999999</v>
+        <v>0.8527</v>
       </c>
     </row>
     <row r="53">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>29.13</v>
+        <v>29.18</v>
       </c>
       <c r="C53" t="n">
-        <v>0.9085</v>
+        <v>0.9099</v>
       </c>
     </row>
     <row r="54">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>22.53</v>
+        <v>22.55</v>
       </c>
       <c r="C54" t="n">
-        <v>0.7336</v>
+        <v>0.7349</v>
       </c>
     </row>
     <row r="55">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>21.26</v>
+        <v>21.28</v>
       </c>
       <c r="C55" t="n">
-        <v>0.6556999999999999</v>
+        <v>0.6572</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>32.99</v>
+        <v>33.17</v>
       </c>
       <c r="C56" t="n">
-        <v>0.9463</v>
+        <v>0.9483</v>
       </c>
     </row>
     <row r="57">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25.18</v>
+        <v>25.23</v>
       </c>
       <c r="C57" t="n">
-        <v>0.7882</v>
+        <v>0.7905</v>
       </c>
     </row>
     <row r="58">
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>31.1</v>
+        <v>31.23</v>
       </c>
       <c r="C58" t="n">
-        <v>0.8971</v>
+        <v>0.9002</v>
       </c>
     </row>
     <row r="59">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>26.04</v>
+        <v>26.1</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8646</v>
+        <v>0.8663999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>22.05</v>
+        <v>22.18</v>
       </c>
       <c r="C60" t="n">
-        <v>0.7621</v>
+        <v>0.7674</v>
       </c>
     </row>
     <row r="61">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>22.61</v>
+        <v>22.64</v>
       </c>
       <c r="C61" t="n">
-        <v>0.5711000000000001</v>
+        <v>0.5738</v>
       </c>
     </row>
     <row r="62">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>24.8</v>
+        <v>24.84</v>
       </c>
       <c r="C62" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.762</v>
       </c>
     </row>
     <row r="63">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>21.96</v>
+        <v>21.98</v>
       </c>
       <c r="C63" t="n">
-        <v>0.8145</v>
+        <v>0.8174</v>
       </c>
     </row>
     <row r="64">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>22.43</v>
+        <v>22.52</v>
       </c>
       <c r="C64" t="n">
-        <v>0.6213</v>
+        <v>0.6236</v>
       </c>
     </row>
     <row r="65">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>26.71</v>
+        <v>26.75</v>
       </c>
       <c r="C65" t="n">
-        <v>0.7879</v>
+        <v>0.7895</v>
       </c>
     </row>
     <row r="66">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>25.42</v>
+        <v>25.48</v>
       </c>
       <c r="C66" t="n">
-        <v>0.7246</v>
+        <v>0.728</v>
       </c>
     </row>
     <row r="67">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>22.25</v>
+        <v>22.27</v>
       </c>
       <c r="C67" t="n">
-        <v>0.6435</v>
+        <v>0.6449</v>
       </c>
     </row>
     <row r="68">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>20.5</v>
+        <v>20.56</v>
       </c>
       <c r="C68" t="n">
-        <v>0.8875999999999999</v>
+        <v>0.8903</v>
       </c>
     </row>
     <row r="69">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>30.41</v>
+        <v>30.55</v>
       </c>
       <c r="C69" t="n">
-        <v>0.8851</v>
+        <v>0.8885999999999999</v>
       </c>
     </row>
     <row r="70">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>24.84</v>
+        <v>24.86</v>
       </c>
       <c r="C70" t="n">
-        <v>0.7553</v>
+        <v>0.7571</v>
       </c>
     </row>
     <row r="71">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>22.18</v>
+        <v>22.2</v>
       </c>
       <c r="C71" t="n">
-        <v>0.5968</v>
+        <v>0.5982</v>
       </c>
     </row>
     <row r="72">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>28.02</v>
+        <v>28.07</v>
       </c>
       <c r="C72" t="n">
-        <v>0.6645</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="73">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>20.4</v>
+        <v>20.46</v>
       </c>
       <c r="C73" t="n">
-        <v>0.8254</v>
+        <v>0.8284</v>
       </c>
     </row>
     <row r="74">
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>19.99</v>
+        <v>20.2</v>
       </c>
       <c r="C74" t="n">
-        <v>0.5737</v>
+        <v>0.5789</v>
       </c>
     </row>
     <row r="75">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>23.79</v>
+        <v>23.83</v>
       </c>
       <c r="C75" t="n">
-        <v>0.7037</v>
+        <v>0.7073</v>
       </c>
     </row>
     <row r="76">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>31.69</v>
+        <v>31.76</v>
       </c>
       <c r="C76" t="n">
-        <v>0.8862</v>
+        <v>0.8872</v>
       </c>
     </row>
     <row r="77">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>23.06</v>
+        <v>23.02</v>
       </c>
       <c r="C77" t="n">
-        <v>0.7376</v>
+        <v>0.7381</v>
       </c>
     </row>
     <row r="78">
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>22.74</v>
+        <v>22.75</v>
       </c>
       <c r="C78" t="n">
-        <v>0.6754</v>
+        <v>0.6768999999999999</v>
       </c>
     </row>
     <row r="79">
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>27.39</v>
+        <v>27.45</v>
       </c>
       <c r="C79" t="n">
-        <v>0.7724</v>
+        <v>0.7741</v>
       </c>
     </row>
     <row r="80">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>25.51</v>
+        <v>25.55</v>
       </c>
       <c r="C80" t="n">
-        <v>0.6992</v>
+        <v>0.701</v>
       </c>
     </row>
     <row r="81">
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>35.8</v>
+        <v>35.85</v>
       </c>
       <c r="C81" t="n">
-        <v>0.9536</v>
+        <v>0.9542</v>
       </c>
     </row>
     <row r="82">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>37.55</v>
+        <v>37.69</v>
       </c>
       <c r="C82" t="n">
-        <v>0.9711</v>
+        <v>0.9724</v>
       </c>
     </row>
     <row r="83">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>33.02</v>
+        <v>33.17</v>
       </c>
       <c r="C83" t="n">
-        <v>0.9426</v>
+        <v>0.9433</v>
       </c>
     </row>
     <row r="84">
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>22.28</v>
+        <v>22.32</v>
       </c>
       <c r="C84" t="n">
-        <v>0.7</v>
+        <v>0.7025</v>
       </c>
     </row>
     <row r="85">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>28.7</v>
+        <v>28.75</v>
       </c>
       <c r="C85" t="n">
-        <v>0.8118</v>
+        <v>0.8135</v>
       </c>
     </row>
     <row r="86">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>28.38</v>
+        <v>28.45</v>
       </c>
       <c r="C86" t="n">
-        <v>0.9033</v>
+        <v>0.9049</v>
       </c>
     </row>
     <row r="87">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>30.59</v>
+        <v>30.58</v>
       </c>
       <c r="C87" t="n">
-        <v>0.8862</v>
+        <v>0.8868</v>
       </c>
     </row>
     <row r="88">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>27.89</v>
+        <v>27.94</v>
       </c>
       <c r="C88" t="n">
-        <v>0.886</v>
+        <v>0.8877</v>
       </c>
     </row>
     <row r="89">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>19.9</v>
+        <v>19.92</v>
       </c>
       <c r="C89" t="n">
-        <v>0.5732</v>
+        <v>0.5764</v>
       </c>
     </row>
     <row r="90">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>26.79</v>
+        <v>26.82</v>
       </c>
       <c r="C90" t="n">
-        <v>0.7171</v>
+        <v>0.7191</v>
       </c>
     </row>
     <row r="91">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>38.34</v>
+        <v>38.51</v>
       </c>
       <c r="C91" t="n">
-        <v>0.9764</v>
+        <v>0.9771</v>
       </c>
     </row>
     <row r="92">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>24.04</v>
+        <v>24.06</v>
       </c>
       <c r="C92" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.6871</v>
       </c>
     </row>
     <row r="93">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>18.91</v>
+        <v>18.98</v>
       </c>
       <c r="C93" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.6572</v>
       </c>
     </row>
     <row r="94">
@@ -1651,7 +1651,7 @@
         <v>28.59</v>
       </c>
       <c r="C94" t="n">
-        <v>0.9233</v>
+        <v>0.9237</v>
       </c>
     </row>
     <row r="95">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>27.23</v>
+        <v>27.25</v>
       </c>
       <c r="C95" t="n">
-        <v>0.7853</v>
+        <v>0.7869</v>
       </c>
     </row>
     <row r="96">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>20.16</v>
+        <v>20.15</v>
       </c>
       <c r="C96" t="n">
-        <v>0.4492</v>
+        <v>0.4504</v>
       </c>
     </row>
     <row r="97">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>25.6</v>
+        <v>25.58</v>
       </c>
       <c r="C97" t="n">
-        <v>0.8719</v>
+        <v>0.8739</v>
       </c>
     </row>
     <row r="98">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>25.02</v>
+        <v>25.06</v>
       </c>
       <c r="C98" t="n">
-        <v>0.7688</v>
+        <v>0.7709</v>
       </c>
     </row>
     <row r="99">
@@ -1716,7 +1716,7 @@
         <v>20.69</v>
       </c>
       <c r="C99" t="n">
-        <v>0.5317</v>
+        <v>0.5343</v>
       </c>
     </row>
     <row r="100">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>26.12</v>
+        <v>26.27</v>
       </c>
       <c r="C100" t="n">
-        <v>0.8022</v>
+        <v>0.8080000000000001</v>
       </c>
     </row>
     <row r="101">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>26.36</v>
+        <v>26.41</v>
       </c>
       <c r="C101" t="n">
-        <v>0.7497</v>
+        <v>0.7512</v>
       </c>
     </row>
     <row r="102">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>26.13</v>
+        <v>26.19</v>
       </c>
       <c r="C102" t="n">
-        <v>0.7864</v>
+        <v>0.7884</v>
       </c>
     </row>
   </sheetData>
